--- a/ftse_structure_live.xlsx
+++ b/ftse_structure_live.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39 UK</t>
+          <t>2026-10-22 17:08 UK</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>

--- a/ftse_structure_live.xlsx
+++ b/ftse_structure_live.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 17:08 UK</t>
+          <t>2026-10-23 17:08 UK</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>

--- a/ftse_structure_live.xlsx
+++ b/ftse_structure_live.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 17:08 UK</t>
+          <t>2026-10-23 20:17 UK</t>
         </is>
       </c>
     </row>

--- a/ftse_structure_live.xlsx
+++ b/ftse_structure_live.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 20:17 UK</t>
+          <t>2026-10-26 17:09 UK</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Measured-move target: closed trades</t>
+          <t>Recovered signals (included in totals)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -512,7 +512,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Measured-move target: total after costs (£)</t>
+          <t>Measured-move target: closed trades</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -522,29 +522,29 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Measured-move target: average per trade (£)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>none yet</t>
-        </is>
+          <t>Measured-move target: total after costs (£)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2x stop target: closed trades</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>0</v>
+          <t>Measured-move target: average per trade (£)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>none yet</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2x stop target: total after costs (£)</t>
+          <t>2x stop target: closed trades</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -554,17 +554,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>2x stop target: total after costs (£)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>2x stop target: average per trade (£)</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>none yet</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Rules as backtested: an impulse of large up days in an uptrend, a 38.2-61.8% pullback, then a strong up day closing above the previous 3 days' highs. Bought at the next open; stop below the pullback. Two exits tracked on the same trade. Costs £1.50 per £250 (IG share dealing). Only about 6-20 signals a year are expected, so judge it over many months. Paper trading only.</t>
         </is>
@@ -581,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -606,6 +616,7 @@
     <col width="15" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
     <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,6 +730,11 @@
           <t>After costs, 2x (£)</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>When recorded</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ftse_structure_live.xlsx
+++ b/ftse_structure_live.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26 17:09 UK</t>
+          <t>2026-10-26 20:32 UK</t>
         </is>
       </c>
     </row>

--- a/ftse_structure_live.xlsx
+++ b/ftse_structure_live.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26 20:32 UK</t>
+          <t>2026-10-26 20:46 UK</t>
         </is>
       </c>
     </row>

--- a/ftse_structure_live.xlsx
+++ b/ftse_structure_live.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26 20:46 UK</t>
+          <t>2026-10-27 17:07 UK</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>

--- a/ftse_structure_live.xlsx
+++ b/ftse_structure_live.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27 17:07 UK</t>
+          <t>2026-10-27 21:30 UK</t>
         </is>
       </c>
     </row>

--- a/ftse_structure_live.xlsx
+++ b/ftse_structure_live.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27 21:30 UK</t>
+          <t>2026-10-27 21:42 UK</t>
         </is>
       </c>
     </row>

--- a/ftse_structure_live.xlsx
+++ b/ftse_structure_live.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27 21:42 UK</t>
+          <t>2026-10-28 17:08 UK</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>

--- a/ftse_structure_live.xlsx
+++ b/ftse_structure_live.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28 17:08 UK</t>
+          <t>2026-10-28 20:32 UK</t>
         </is>
       </c>
     </row>

--- a/ftse_structure_live.xlsx
+++ b/ftse_structure_live.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28 20:32 UK</t>
+          <t>2026-10-29 17:07 UK</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>

--- a/ftse_structure_live.xlsx
+++ b/ftse_structure_live.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29 17:07 UK</t>
+          <t>2026-10-30 17:07 UK</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
